--- a/output/pdf_financials_xlsx/TMAS.xlsx
+++ b/output/pdf_financials_xlsx/TMAS.xlsx
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.901622</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.307335</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.54671</v>
       </c>
     </row>
     <row r="93">
@@ -3112,7 +3112,11 @@
           <t>Reserves 8, 13</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3623,7 +3627,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>4.901622</v>
       </c>

--- a/output/pdf_financials_xlsx/TMAS.xlsx
+++ b/output/pdf_financials_xlsx/TMAS.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.708382</v>
+        <v>0.914477</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.406513</v>
+        <v>1.740448</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.94277</v>
+        <v>5.668111</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.708382</v>
+        <v>-0.914477</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.406513</v>
+        <v>-1.740448</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.94277</v>
+        <v>-5.668111</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003105</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022476</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.233151</v>
+        <v>-2.230046</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.752535</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.752535</v>
+        <v>-1.730059</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.233151</v>
+        <v>-2.230046</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.752535</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.752535</v>
+        <v>-1.730059</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.271236</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.07656200000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.704835</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.271236</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.07656200000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.704835</v>
       </c>
     </row>
     <row r="37">
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.157772</v>
+        <v>0.08121</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.938492</v>
+        <v>0.233657</v>
       </c>
     </row>
     <row r="49">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
